--- a/05-automation-vba/02-vba-fundamentals/5.2-vba-fundamentals.xlsx
+++ b/05-automation-vba/02-vba-fundamentals/5.2-vba-fundamentals.xlsx
@@ -227,7 +227,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="52">
+  <cellXfs count="51">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -320,9 +320,6 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="1" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="1" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -330,13 +327,13 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="166" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -870,7 +867,7 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="33" customHeight="1">
+    <row r="15" ht="18" customHeight="1">
       <c r="B15" s="8" t="inlineStr">
         <is>
           <t>3. Check yourself</t>
@@ -878,7 +875,7 @@
       </c>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>The Check column shows ✔ Correct (green) or ✘ Not yet (red). Tasks marked 'See key' are checked by comparing with the answer key.</t>
+          <t>The Check column shows ✔ Correct (green) or ✘ Not yet (red).</t>
         </is>
       </c>
     </row>
@@ -983,7 +980,7 @@
       </c>
       <c r="C25" s="7" t="inlineStr">
         <is>
-          <t>Pre-filled summary formula — it reads the work you did on another sheet.</t>
+          <t>Pre-filled summary formula. It reads the work you did on another sheet, so don't type over it.</t>
         </is>
       </c>
     </row>
@@ -1007,7 +1004,7 @@
       </c>
       <c r="C27" s="7" t="inlineStr">
         <is>
-          <t>Not matching yet — check the hint and try again.</t>
+          <t>Not matching yet. Check the hint and try again.</t>
         </is>
       </c>
     </row>
@@ -1028,7 +1025,7 @@
       </c>
       <c r="C30" s="7" t="inlineStr">
         <is>
-          <t>Data: 505 rows — Excel Table 'tblLabs'</t>
+          <t>Data: 505 rows, in the Excel Table 'tblLabs'</t>
         </is>
       </c>
     </row>
@@ -1390,7 +1387,7 @@
         </is>
       </c>
       <c r="D16" cm="1" s="21">
-        <f t="array" ref="D16">IF(COUNTA('Labs'!M2:M506)=0,"",COUNTIF('Labs'!M2:M506,"SLOW"))</f>
+        <f t="array" ref="D16">IF(COUNTA(Labs!M2:M506)=0,"",COUNTIF(Labs!M2:M506,"SLOW"))</f>
         <v/>
       </c>
       <c r="E16" s="22">
@@ -29064,7 +29061,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="154" customHeight="1">
+    <row r="2" ht="124" customHeight="1">
       <c r="A2" s="14" t="inlineStr">
         <is>
           <t>The ICU medical director wants a one-click 'lab snapshot' for the morning huddle. Complete the LabSnapshot stub in the starter module so that it does four things:
@@ -29301,7 +29298,7 @@
     <col width="55" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="48" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
     <col width="62" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
@@ -29315,7 +29312,7 @@
     <row r="2" ht="32" customHeight="1">
       <c r="A2" s="28" t="inlineStr">
         <is>
-          <t>Spoiler alert — try every task before reading this sheet. Column C is the value the Check column compares against. Column D is a sample solution; column E is that same formula, live, proving it works.</t>
+          <t>Spoiler alert: try every task before reading this sheet. Column C is the value the Check column compares against. Column D is a sample solution, and column E recalculates a formula for it live, proving the answer.</t>
         </is>
       </c>
     </row>
@@ -29377,8 +29374,8 @@
 End Sub</t>
         </is>
       </c>
-      <c r="E5" cm="1" s="46">
-        <f t="array" ref="E5">COUNTA('Labs'!A2:A506)</f>
+      <c r="E5" cm="1" s="19">
+        <f t="array" ref="E5">COUNTA(Labs!A2:A506)</f>
         <v/>
       </c>
       <c r="F5" s="19" t="inlineStr">
@@ -29401,7 +29398,7 @@
       <c r="C6" s="44" t="n">
         <v>5</v>
       </c>
-      <c r="D6" s="47" t="inlineStr">
+      <c r="D6" s="46" t="inlineStr">
         <is>
           <t>Trace it: drawCount is set to 5. The next line assigns to drawCuont, which is a different variable, so drawCount is still 5 when it's printed.</t>
         </is>
@@ -29433,7 +29430,7 @@
           <t>6</t>
         </is>
       </c>
-      <c r="D7" s="47" t="inlineStr">
+      <c r="D7" s="46" t="inlineStr">
         <is>
           <t>Run-time error 6: Overflow. An Integer holds only −32,768 to 32,767, and 51,527 is bigger.</t>
         </is>
@@ -29465,7 +29462,7 @@
           <t>3 h 19 min</t>
         </is>
       </c>
-      <c r="D8" s="47" t="inlineStr">
+      <c r="D8" s="46" t="inlineStr">
         <is>
           <t>199 \ 60 is 3 (whole hours) and 199 Mod 60 is 19 (leftover minutes). &amp; joins everything into one string: 3 h 19 min.</t>
         </is>
@@ -29495,7 +29492,7 @@
       <c r="C9" s="44" t="n">
         <v>24</v>
       </c>
-      <c r="D9" s="47" t="inlineStr">
+      <c r="D9" s="46" t="inlineStr">
         <is>
           <t>The loop body runs for hr = 0, 4, 8, 12, 16, 20 (6 checks). Next then adds the Step again (20 + 4 = 24), which is past 23, so the loop ends with hr = 24.</t>
         </is>
@@ -29527,7 +29524,7 @@
           <t>Elevated</t>
         </is>
       </c>
-      <c r="D10" s="47" t="inlineStr">
+      <c r="D10" s="46" t="inlineStr">
         <is>
           <t>4.6 is not &lt; 0.5 and not ≤ 2, but it is &gt; 2, so Case Is &gt; 2 matches and sets Elevated. VBA then jumps to End Select, so Case Is &gt; 4 is never tested.</t>
         </is>
@@ -29543,7 +29540,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="81" customHeight="1">
+    <row r="11" ht="66" customHeight="1">
       <c r="A11" s="18" t="inlineStr">
         <is>
           <t>7</t>
@@ -29557,7 +29554,7 @@
       <c r="C11" s="44" t="n">
         <v>18</v>
       </c>
-      <c r="D11" s="47" t="inlineStr">
+      <c r="D11" s="46" t="inlineStr">
         <is>
           <t>level 400 → 200 (6 h) → 100 (12 h) → 50 (18 h). Before the next pass VBA tests 50 &gt; 50, which is False, so the loop stops: 18.</t>
         </is>
@@ -29606,13 +29603,13 @@
 End Sub</t>
         </is>
       </c>
-      <c r="E12" cm="1" s="46">
-        <f t="array" ref="E12">COUNTIF('Labs'!I2:I506,"HH")+COUNTIF('Labs'!I2:I506,"LL")</f>
+      <c r="E12" cm="1" s="19">
+        <f t="array" ref="E12">COUNTIF(Labs!I2:I506,"HH")+COUNTIF(Labs!I2:I506,"LL")</f>
         <v/>
       </c>
       <c r="F12" s="19" t="inlineStr">
         <is>
-          <t>This is the counter pattern: start a Long at 0 and add 1 each time a condition is true. Each Or side must be a full comparison: cell.Value = "HH" Or cell.Value = "LL". Writing cell.Value = "HH" Or "LL" gives a Type mismatch error. Cross-check with a formula: =COUNTIF('Labs'!I2:I506,"HH")+COUNTIF('Labs'!I2:I506,"LL").</t>
+          <t>This is the counter pattern: start a Long at 0 and add 1 each time a condition is true. Each Or side must be a full comparison: cell.Value = "HH" Or cell.Value = "LL". Writing cell.Value = "HH" Or "LL" gives a Type mismatch error. Cross-check with a formula: =COUNTIF(Labs!I2:I506,"HH")+COUNTIF(Labs!I2:I506,"LL").</t>
         </is>
       </c>
     </row>
@@ -29627,7 +29624,7 @@
           <t>Complete AveragePotassium: loop over the rows with For…Next, add up ResultValue for every potassium result (TestCode K) and count them, then write the average to Output!B7. (Full precision or 2 decimal places are both accepted.)</t>
         </is>
       </c>
-      <c r="C13" s="48" t="n">
+      <c r="C13" s="47" t="n">
         <v>4.070833333333334</v>
       </c>
       <c r="D13" s="45" t="inlineStr">
@@ -29653,8 +29650,8 @@
 End Sub</t>
         </is>
       </c>
-      <c r="E13" cm="1" s="49">
-        <f t="array" ref="E13">AVERAGEIF('Labs'!C2:C506,"K",'Labs'!E2:E506)</f>
+      <c r="E13" cm="1" s="48">
+        <f t="array" ref="E13">AVERAGEIF(Labs!C2:C506,"K",Labs!E2:E506)</f>
         <v/>
       </c>
       <c r="F13" s="19" t="inlineStr">
@@ -29700,8 +29697,8 @@
 End Sub</t>
         </is>
       </c>
-      <c r="E14" cm="1" s="46">
-        <f t="array" ref="E14">INDEX('Labs'!A2:A506,MIN(IFERROR(MATCH("HH",'Labs'!I2:I506,0),99999),IFERROR(MATCH("LL",'Labs'!I2:I506,0),99999)))</f>
+      <c r="E14" cm="1" s="19">
+        <f t="array" ref="E14">INDEX(Labs!A2:A506,MIN(IFERROR(MATCH("HH",Labs!I2:I506,0),99999),IFERROR(MATCH("LL",Labs!I2:I506,0),99999)))</f>
         <v/>
       </c>
       <c r="F14" s="19" t="inlineStr">
@@ -29747,8 +29744,8 @@
 End Sub</t>
         </is>
       </c>
-      <c r="E15" cm="1" s="46">
-        <f t="array" ref="E15">SUMPRODUCT(('Labs'!J2:J506="STAT")*(ROUND(('Labs'!L2:L506-'Labs'!K2:K506)*1440,0)&gt;60))</f>
+      <c r="E15" cm="1" s="19">
+        <f t="array" ref="E15">SUMPRODUCT((Labs!J2:J506="STAT")*(ROUND((Labs!L2:L506-Labs!K2:K506)*1440,0)&gt;60))</f>
         <v/>
       </c>
       <c r="F15" s="19" t="inlineStr">
@@ -29797,8 +29794,8 @@
 End Sub</t>
         </is>
       </c>
-      <c r="E16" cm="1" s="46">
-        <f t="array" ref="E16">COUNTIFS('Labs'!C2:C506,"CREAT",'Labs'!E2:E506,"&gt;2")</f>
+      <c r="E16" cm="1" s="19">
+        <f t="array" ref="E16">COUNTIFS(Labs!C2:C506,"CREAT",Labs!E2:E506,"&gt;2")</f>
         <v/>
       </c>
       <c r="F16" s="19" t="inlineStr">
@@ -29838,8 +29835,8 @@
 End Sub</t>
         </is>
       </c>
-      <c r="E17" cm="1" s="46">
-        <f t="array" ref="E17">COUNTIFS('Labs'!C2:C506,"GLU",'Labs'!E2:E506,"&gt;180")</f>
+      <c r="E17" cm="1" s="19">
+        <f t="array" ref="E17">COUNTIFS(Labs!C2:C506,"GLU",Labs!E2:E506,"&gt;180")</f>
         <v/>
       </c>
       <c r="F17" s="19" t="inlineStr">
@@ -29871,7 +29868,7 @@
     <col width="55" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="48" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
     <col width="62" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
@@ -29885,7 +29882,7 @@
     <row r="2" ht="32" customHeight="1">
       <c r="A2" s="28" t="inlineStr">
         <is>
-          <t>Spoiler alert — try every task before reading this sheet. Column C is the value the Check column compares against. Column D is a sample solution; column E is that same formula, live, proving it works.</t>
+          <t>Spoiler alert: try every task before reading this sheet. Column C is the value the Check column compares against. Column D is a sample solution, and column E recalculates a formula for it live, proving the answer.</t>
         </is>
       </c>
     </row>
@@ -30000,8 +29997,8 @@
 End Sub</t>
         </is>
       </c>
-      <c r="E5" cm="1" s="46">
-        <f t="array" ref="E5">COUNTIF('Labs'!I2:I506,"H")+COUNTIF('Labs'!I2:I506,"L")</f>
+      <c r="E5" cm="1" s="19">
+        <f t="array" ref="E5">COUNTIF(Labs!I2:I506,"H")+COUNTIF(Labs!I2:I506,"L")</f>
         <v/>
       </c>
       <c r="F5" s="19" t="inlineStr">
@@ -30024,13 +30021,13 @@
       <c r="C6" s="44" t="n">
         <v>10</v>
       </c>
-      <c r="D6" s="47" t="inlineStr">
+      <c r="D6" s="46" t="inlineStr">
         <is>
           <t>Run LabSnapshot (full code in B1). The gray cell uses =COUNTA(Output!E5:E40).</t>
         </is>
       </c>
-      <c r="E6" cm="1" s="46">
-        <f t="array" ref="E6">SUMPRODUCT(1/COUNTIF('Labs'!C2:C506,'Labs'!C2:C506))</f>
+      <c r="E6" cm="1" s="19">
+        <f t="array" ref="E6">SUMPRODUCT(1/COUNTIF(Labs!C2:C506,Labs!C2:C506))</f>
         <v/>
       </c>
       <c r="F6" s="19" t="inlineStr">
@@ -30053,13 +30050,13 @@
       <c r="C7" s="44" t="n">
         <v>40</v>
       </c>
-      <c r="D7" s="47" t="inlineStr">
+      <c r="D7" s="46" t="inlineStr">
         <is>
           <t>Run LabSnapshot. The gray cell uses =INDEX(Output!G5:G40,MATCH("CREAT",Output!E5:E40,0)).</t>
         </is>
       </c>
-      <c r="E7" cm="1" s="46">
-        <f t="array" ref="E7">COUNTIFS('Labs'!C2:C506,"CREAT",'Labs'!I2:I506,"&lt;&gt;N")</f>
+      <c r="E7" cm="1" s="19">
+        <f t="array" ref="E7">COUNTIFS(Labs!C2:C506,"CREAT",Labs!I2:I506,"&lt;&gt;N")</f>
         <v/>
       </c>
       <c r="F7" s="19" t="inlineStr">
@@ -30079,16 +30076,16 @@
           <t>What percentage of lactate (LACT) results are abnormal? (The gray cell looks up LACT in your table.)</t>
         </is>
       </c>
-      <c r="C8" s="50" t="n">
+      <c r="C8" s="49" t="n">
         <v>0.7692307692307693</v>
       </c>
-      <c r="D8" s="47" t="inlineStr">
+      <c r="D8" s="46" t="inlineStr">
         <is>
           <t>Run LabSnapshot. The gray cell uses =INDEX(Output!H5:H40,MATCH("LACT",Output!E5:E40,0)).</t>
         </is>
       </c>
-      <c r="E8" cm="1" s="51">
-        <f t="array" ref="E8">COUNTIFS('Labs'!C2:C506,"LACT",'Labs'!I2:I506,"&lt;&gt;N")/COUNTIF('Labs'!C2:C506,"LACT")</f>
+      <c r="E8" cm="1" s="50">
+        <f t="array" ref="E8">COUNTIFS(Labs!C2:C506,"LACT",Labs!I2:I506,"&lt;&gt;N")/COUNTIF(Labs!C2:C506,"LACT")</f>
         <v/>
       </c>
       <c r="F8" s="19" t="inlineStr">
@@ -30113,7 +30110,7 @@
           <t>GLU</t>
         </is>
       </c>
-      <c r="D9" s="47" t="inlineStr">
+      <c r="D9" s="46" t="inlineStr">
         <is>
           <t>Run LabSnapshot. Step 5 keeps the best value so far in topPct and its code in topCode.</t>
         </is>

--- a/05-automation-vba/02-vba-fundamentals/5.2-vba-fundamentals.xlsx
+++ b/05-automation-vba/02-vba-fundamentals/5.2-vba-fundamentals.xlsx
@@ -773,7 +773,7 @@
     <row r="4">
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Expert  ·  about 60 minutes  ·  Bluestone Health System (fictional)</t>
+          <t>Expert  ·  about 160 minutes  ·  Bluestone Health System (fictional)</t>
         </is>
       </c>
     </row>
@@ -1020,41 +1020,63 @@
     <row r="30" ht="18" customHeight="1">
       <c r="B30" s="8" t="inlineStr">
         <is>
+          <t>Practice</t>
+        </is>
+      </c>
+      <c r="C30" s="7" t="inlineStr">
+        <is>
+          <t>13 practice tasks, each with a Check cell.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="18" customHeight="1">
+      <c r="B31" s="8" t="inlineStr">
+        <is>
           <t>Labs</t>
         </is>
       </c>
-      <c r="C30" s="7" t="inlineStr">
+      <c r="C31" s="7" t="inlineStr">
         <is>
           <t>Data: 505 rows, in the Excel Table 'tblLabs'</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="33" customHeight="1">
-      <c r="B31" s="8" t="inlineStr">
-        <is>
-          <t>About the data</t>
-        </is>
-      </c>
-      <c r="C31" s="7" t="inlineStr">
-        <is>
-          <t>505 lab results from Bluestone's three intensive care units (Bluestone Memorial, Ashby Falls, Cedar Ridge), collected January–April 2025 and listed in the order the results were released.</t>
         </is>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
       <c r="B32" s="8" t="inlineStr">
         <is>
+          <t>Bonus</t>
+        </is>
+      </c>
+      <c r="C32" s="7" t="inlineStr">
+        <is>
+          <t>The bonus challenge (5 parts).</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="33" customHeight="1">
+      <c r="B33" s="8" t="inlineStr">
+        <is>
+          <t>About the data</t>
+        </is>
+      </c>
+      <c r="C33" s="7" t="inlineStr">
+        <is>
+          <t>505 lab results from Bluestone's three intensive care units (Bluestone Memorial, Ashby Falls, Cedar Ridge), collected January–April 2025 and listed in the order the results were released.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="18" customHeight="1">
+      <c r="B34" s="8" t="inlineStr">
+        <is>
           <t>Disclaimer</t>
         </is>
       </c>
-      <c r="C32" s="7" t="inlineStr">
+      <c r="C34" s="7" t="inlineStr">
         <is>
           <t>All people, places, and numbers are synthetic and fictional. Not clinical guidance.</t>
         </is>
       </c>
     </row>
-    <row r="33"/>
-    <row r="34"/>
     <row r="35"/>
     <row r="36"/>
     <row r="37"/>

--- a/05-automation-vba/02-vba-fundamentals/5.2-vba-fundamentals.xlsx
+++ b/05-automation-vba/02-vba-fundamentals/5.2-vba-fundamentals.xlsx
@@ -747,7 +747,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:C40"/>
+  <dimension ref="B2:C35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -755,7 +755,6 @@
     <col width="95" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
-    <row r="1"/>
     <row r="2">
       <c r="B2" s="1" t="inlineStr">
         <is>
@@ -777,7 +776,6 @@
         </is>
       </c>
     </row>
-    <row r="5"/>
     <row r="6">
       <c r="B6" s="4" t="inlineStr">
         <is>
@@ -834,7 +832,6 @@
         </is>
       </c>
     </row>
-    <row r="11"/>
     <row r="12">
       <c r="B12" s="4" t="inlineStr">
         <is>
@@ -855,7 +852,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="18" customHeight="1">
+    <row r="14" ht="33" customHeight="1">
       <c r="B14" s="8" t="inlineStr">
         <is>
           <t>2. Practice</t>
@@ -863,7 +860,7 @@
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
-          <t>Go to the 'Practice' sheet. Type your answer in each yellow cell, or run the task's macro so its gray cell fills in by itself.</t>
+          <t>Go to the 'Practice' sheet. Type your predictions for tasks 2–7 in the yellow cells. For tasks 1 and 8–13, run your macros. Their gray cells fill in by themselves.</t>
         </is>
       </c>
     </row>
@@ -915,7 +912,7 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="33" customHeight="1">
+    <row r="19" ht="48" customHeight="1">
       <c r="B19" s="8" t="inlineStr">
         <is>
           <t>Note</t>
@@ -923,7 +920,7 @@
       </c>
       <c r="C19" s="7" t="inlineStr">
         <is>
-          <t>Import starter/LabMacros.bas and starter/Snippets.bas from the lesson folder: open the Visual Basic Editor (Alt+F11; Mac: Option+F11 or Developer → Visual Basic), then File → Import File…</t>
+          <t>Import starter/LabMacros.bas and starter/Snippets.bas from the lesson folder: open the Visual Basic Editor with Alt + F11 (Mac: Option + F11, or Developer → Visual Basic), then choose File → Import File…</t>
         </is>
       </c>
     </row>
@@ -935,97 +932,95 @@
       </c>
       <c r="C20" s="7" t="inlineStr">
         <is>
-          <t>Debug.Print writes to the Immediate window. Open it in the Visual Basic Editor with Ctrl+G (Mac: View → Immediate Window) before you run the snippets.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="33" customHeight="1">
-      <c r="B21" s="8" t="inlineStr">
-        <is>
-          <t>Note</t>
-        </is>
-      </c>
-      <c r="C21" s="7" t="inlineStr">
-        <is>
-          <t>The Snippets sheet shows the code for the predict-the-output tasks. The Output sheet is where your macros write their results.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22"/>
-    <row r="23">
-      <c r="B23" s="4" t="inlineStr">
+          <t>Debug.Print writes to the Immediate window. Open it in the Visual Basic Editor with Ctrl + G (Mac: View → Immediate Window) before you run the snippets.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" s="4" t="inlineStr">
         <is>
           <t>Color legend</t>
         </is>
       </c>
-      <c r="C23" s="5" t="n"/>
+      <c r="C22" s="5" t="n"/>
+    </row>
+    <row r="23" ht="18" customHeight="1">
+      <c r="B23" s="9" t="inlineStr">
+        <is>
+          <t>Yellow cell</t>
+        </is>
+      </c>
+      <c r="C23" s="7" t="inlineStr">
+        <is>
+          <t>Your answer goes here.</t>
+        </is>
+      </c>
     </row>
     <row r="24" ht="18" customHeight="1">
-      <c r="B24" s="9" t="inlineStr">
-        <is>
-          <t>Yellow cell</t>
+      <c r="B24" s="10" t="inlineStr">
+        <is>
+          <t>Gray cell</t>
         </is>
       </c>
       <c r="C24" s="7" t="inlineStr">
         <is>
-          <t>Your answer goes here.</t>
+          <t>Pre-filled summary formula. It reads the work you did on another sheet, so don't type over it.</t>
         </is>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
-      <c r="B25" s="10" t="inlineStr">
-        <is>
-          <t>Gray cell</t>
+      <c r="B25" s="11" t="inlineStr">
+        <is>
+          <t>✔ Correct</t>
         </is>
       </c>
       <c r="C25" s="7" t="inlineStr">
         <is>
-          <t>Pre-filled summary formula. It reads the work you did on another sheet, so don't type over it.</t>
+          <t>Your answer matches the key.</t>
         </is>
       </c>
     </row>
     <row r="26" ht="18" customHeight="1">
-      <c r="B26" s="11" t="inlineStr">
-        <is>
-          <t>✔ Correct</t>
+      <c r="B26" s="12" t="inlineStr">
+        <is>
+          <t>✘ Not yet</t>
         </is>
       </c>
       <c r="C26" s="7" t="inlineStr">
         <is>
-          <t>Your answer matches the key.</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="18" customHeight="1">
-      <c r="B27" s="12" t="inlineStr">
-        <is>
-          <t>✘ Not yet</t>
-        </is>
-      </c>
-      <c r="C27" s="7" t="inlineStr">
-        <is>
           <t>Not matching yet. Check the hint and try again.</t>
         </is>
       </c>
     </row>
-    <row r="28"/>
-    <row r="29">
-      <c r="B29" s="4" t="inlineStr">
+    <row r="28">
+      <c r="B28" s="4" t="inlineStr">
         <is>
           <t>Sheets in this workbook</t>
         </is>
       </c>
-      <c r="C29" s="5" t="n"/>
+      <c r="C28" s="5" t="n"/>
+    </row>
+    <row r="29" ht="18" customHeight="1">
+      <c r="B29" s="8" t="inlineStr">
+        <is>
+          <t>Practice</t>
+        </is>
+      </c>
+      <c r="C29" s="7" t="inlineStr">
+        <is>
+          <t>13 practice tasks, each with a Check cell.</t>
+        </is>
+      </c>
     </row>
     <row r="30" ht="18" customHeight="1">
       <c r="B30" s="8" t="inlineStr">
         <is>
-          <t>Practice</t>
+          <t>Snippets</t>
         </is>
       </c>
       <c r="C30" s="7" t="inlineStr">
         <is>
-          <t>13 practice tasks, each with a Check cell.</t>
+          <t>The code for the predict-the-output snippets (Practice tasks 2–7). Run it from the Snippets module.</t>
         </is>
       </c>
     </row>
@@ -1041,48 +1036,54 @@
         </is>
       </c>
     </row>
-    <row r="32" ht="18" customHeight="1">
+    <row r="32" ht="33" customHeight="1">
       <c r="B32" s="8" t="inlineStr">
         <is>
+          <t>Output</t>
+        </is>
+      </c>
+      <c r="C32" s="7" t="inlineStr">
+        <is>
+          <t>Where your macros write their results: B5:B10 for the practice macros (task 11 flags Labs column M instead), and E5:H40 and J5 for the bonus.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="18" customHeight="1">
+      <c r="B33" s="8" t="inlineStr">
+        <is>
           <t>Bonus</t>
         </is>
       </c>
-      <c r="C32" s="7" t="inlineStr">
+      <c r="C33" s="7" t="inlineStr">
         <is>
           <t>The bonus challenge (5 parts).</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="33" customHeight="1">
-      <c r="B33" s="8" t="inlineStr">
+    <row r="34" ht="33" customHeight="1">
+      <c r="B34" s="8" t="inlineStr">
         <is>
           <t>About the data</t>
         </is>
       </c>
-      <c r="C33" s="7" t="inlineStr">
+      <c r="C34" s="7" t="inlineStr">
         <is>
           <t>505 lab results from Bluestone's three intensive care units (Bluestone Memorial, Ashby Falls, Cedar Ridge), collected January–April 2025 and listed in the order the results were released.</t>
         </is>
       </c>
     </row>
-    <row r="34" ht="18" customHeight="1">
-      <c r="B34" s="8" t="inlineStr">
+    <row r="35" ht="18" customHeight="1">
+      <c r="B35" s="8" t="inlineStr">
         <is>
           <t>Disclaimer</t>
         </is>
       </c>
-      <c r="C34" s="7" t="inlineStr">
+      <c r="C35" s="7" t="inlineStr">
         <is>
           <t>All people, places, and numbers are synthetic and fictional. Not clinical guidance.</t>
         </is>
       </c>
     </row>
-    <row r="35"/>
-    <row r="36"/>
-    <row r="37"/>
-    <row r="38"/>
-    <row r="39"/>
-    <row r="40"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" fitToHeight="0" fitToWidth="1"/>
@@ -1096,7 +1097,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E40"/>
+  <dimension ref="A1:E18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1116,14 +1117,14 @@
     <row r="2" ht="49" customHeight="1">
       <c r="A2" s="14" t="inlineStr">
         <is>
-          <t>Save this workbook as .xlsm, then import starter/LabMacros.bas and starter/Snippets.bas (VBE → File → Import File…). Tasks 2–7 are predict-the-output questions about the code on the Snippets sheet: type your prediction first, then run the snippet to check it. In tasks 1 and 8–13 you run macros, and the gray cells read what your macros wrote to the Output sheet (or to the TATFlag column on the Labs sheet).</t>
+          <t>Save this workbook as .xlsm, then import starter/LabMacros.bas and starter/Snippets.bas (File → Import File… in the VBE). Tasks 2–7 are predict-the-output questions about the code on the Snippets sheet: type your prediction first, then run the snippet to check it. In tasks 1 and 8–13 you run macros, and the gray cells read what your macros wrote to the Output sheet (or to the TATFlag column on the Labs sheet).</t>
         </is>
       </c>
     </row>
     <row r="3" ht="34" customHeight="1">
       <c r="A3" s="15" t="inlineStr">
         <is>
-          <t>Type your answer in each yellow cell, or run the task's macro so its gray cell fills in by itself. The Check column turns green when your answer matches. Stuck? Read the hint, then the lesson guide. Answers: right-click a sheet tab → Unhide… → 'Answer Key'.</t>
+          <t>Type your predictions for tasks 2–7 in the yellow cells. The gray cells for tasks 1 and 8–13 fill in by themselves when your macros run. The Check column turns green when your answer matches. Stuck? Read the hint, then the lesson guide. Answers: right-click a sheet tab → Unhide… → 'Answer Key'.</t>
         </is>
       </c>
     </row>
@@ -1173,7 +1174,7 @@
       </c>
       <c r="C6" s="20" t="inlineStr">
         <is>
-          <t>Click inside Warmup and press F5, or in Excel press Alt+F8 (Mac: Option+F8), pick Warmup, and click Run</t>
+          <t>Click inside Warmup and press F5, or in Excel press Alt + F8 (Mac: Option + F8), pick Warmup, and click Run</t>
         </is>
       </c>
       <c r="D6" cm="1" s="21">
@@ -1467,28 +1468,6 @@
         <v/>
       </c>
     </row>
-    <row r="19"/>
-    <row r="20"/>
-    <row r="21"/>
-    <row r="22"/>
-    <row r="23"/>
-    <row r="24"/>
-    <row r="25"/>
-    <row r="26"/>
-    <row r="27"/>
-    <row r="28"/>
-    <row r="29"/>
-    <row r="30"/>
-    <row r="31"/>
-    <row r="32"/>
-    <row r="33"/>
-    <row r="34"/>
-    <row r="35"/>
-    <row r="36"/>
-    <row r="37"/>
-    <row r="38"/>
-    <row r="39"/>
-    <row r="40"/>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A2:E2"/>
@@ -1531,7 +1510,7 @@
     <row r="2" ht="48" customHeight="1">
       <c r="A2" s="28" t="inlineStr">
         <is>
-          <t>Predict what each snippet prints, type your prediction on the Practice sheet, then run it from the Snippets module (starter/Snippets.bas) to check. Debug.Print writes to the Immediate window (Ctrl+G; Mac: View → Immediate Window).</t>
+          <t>Predict what each snippet prints, type your prediction on the Practice sheet, then run it from the Snippets module (starter/Snippets.bas) to check. Debug.Print writes to the Immediate window (Ctrl + G; Mac: View → Immediate Window).</t>
         </is>
       </c>
     </row>
@@ -29066,7 +29045,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E40"/>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -29098,7 +29077,7 @@
     <row r="3" ht="34" customHeight="1">
       <c r="A3" s="15" t="inlineStr">
         <is>
-          <t>Type your answer in each yellow cell, or run the task's macro so its gray cell fills in by itself. The Check column turns green when your answer matches. Stuck? Read the hint, then the lesson guide. Answers: right-click a sheet tab → Unhide… → 'Bonus Key'.</t>
+          <t>Type your answer to B1 in its yellow cell. The gray cells for B2–B5 fill in by themselves once LabSnapshot has run. The Check column turns green when your answer matches. Stuck? Read the hint, then the lesson guide. Answers: right-click a sheet tab → Unhide… → 'Bonus Key'.</t>
         </is>
       </c>
     </row>
@@ -29143,7 +29122,7 @@
       </c>
       <c r="B6" s="19" t="inlineStr">
         <is>
-          <t>Run LabSnapshot. Then click the filter arrow on the Labs table's AbnormalFlag header and choose Filter by Color → your amber fill. How many rows are amber? (The status bar shows 'x of 505 records found'.)</t>
+          <t>Run LabSnapshot. Then click the filter arrow on the Labs table's AbnormalFlag header and choose Filter by Color, then your amber fill. How many rows are amber? (The status bar shows 'x of 505 records found'.)</t>
         </is>
       </c>
       <c r="C6" s="20" t="inlineStr">
@@ -29257,36 +29236,6 @@
         <v/>
       </c>
     </row>
-    <row r="11"/>
-    <row r="12"/>
-    <row r="13"/>
-    <row r="14"/>
-    <row r="15"/>
-    <row r="16"/>
-    <row r="17"/>
-    <row r="18"/>
-    <row r="19"/>
-    <row r="20"/>
-    <row r="21"/>
-    <row r="22"/>
-    <row r="23"/>
-    <row r="24"/>
-    <row r="25"/>
-    <row r="26"/>
-    <row r="27"/>
-    <row r="28"/>
-    <row r="29"/>
-    <row r="30"/>
-    <row r="31"/>
-    <row r="32"/>
-    <row r="33"/>
-    <row r="34"/>
-    <row r="35"/>
-    <row r="36"/>
-    <row r="37"/>
-    <row r="38"/>
-    <row r="39"/>
-    <row r="40"/>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A2:E2"/>
@@ -29948,7 +29897,7 @@
       </c>
       <c r="B5" s="19" t="inlineStr">
         <is>
-          <t>Run LabSnapshot. Then click the filter arrow on the Labs table's AbnormalFlag header and choose Filter by Color → your amber fill. How many rows are amber? (The status bar shows 'x of 505 records found'.)</t>
+          <t>Run LabSnapshot. Then click the filter arrow on the Labs table's AbnormalFlag header and choose Filter by Color, then your amber fill. How many rows are amber? (The status bar shows 'x of 505 records found'.)</t>
         </is>
       </c>
       <c r="C5" s="44" t="n">
